--- a/metrics/Metrics_Naive_Model.xlsx
+++ b/metrics/Metrics_Naive_Model.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U4"/>
+  <dimension ref="A1:AS4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,60 +471,180 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>MAE_constant</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>MedAE_constant</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>MSE_constant</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>RMSE_constant</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>R2_constant</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Pearson_constant</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Spearman_constant</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Kendall_constant</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>MAE_stepwise</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>MedAE_stepwise</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>MSE_stepwise</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>RMSE_stepwise</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>R2_stepwise</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Pearson_stepwise</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Spearman_stepwise</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Kendall_stepwise</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>MAE_dynamic</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>MedAE_dynamic</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>MSE_dynamic</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>RMSE_dynamic</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>R2_dynamic</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>Pearson_dynamic</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Spearman_dynamic</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Kendall_dynamic</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
           <t>Int_Conf_R2</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>Int_Conf_RMSE</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>Int_Conf_Pearson</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>Int_Conf_Spearman</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>Int_Conf_Kendall</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>Int_Conf_MAE</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>Int_Conf_MedAE</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>Lag</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>Max_Step</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>Pred_Step</t>
         </is>
@@ -535,67 +655,139 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.776286081487163</v>
+        <v>2.778742793751235</v>
       </c>
       <c r="C2" t="n">
-        <v>2.32576376795391</v>
+        <v>2.380594206247012</v>
       </c>
       <c r="D2" t="n">
-        <v>11.18503280700149</v>
+        <v>11.09680905155252</v>
       </c>
       <c r="E2" t="n">
-        <v>3.344403206403422</v>
+        <v>3.331187333602317</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8597168809463774</v>
+        <v>0.8753637989555831</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9273377129489616</v>
+        <v>0.9358290906602496</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9311716769032105</v>
+        <v>0.9367011663411161</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7745347209228631</v>
+        <v>0.7879521899779102</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01395121863892268</v>
+        <v>4.589048330078348</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1411881118421032</v>
+        <v>5.166732936783513</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4665648135014966</v>
+        <v>25.07960344701707</v>
       </c>
       <c r="M2" t="n">
-        <v>0.4676112477620288</v>
+        <v>5.007954018061375</v>
       </c>
       <c r="N2" t="n">
-        <v>0.3853171935485678</v>
+        <v>0.7305602968112525</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1518105035128057</v>
+        <v>0.9671025662828915</v>
       </c>
       <c r="P2" t="n">
-        <v>0.1775621476704436</v>
-      </c>
-      <c r="Q2" t="inlineStr">
+        <v>0.9770023106870378</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.8871725826644792</v>
+      </c>
+      <c r="R2" t="n">
+        <v>2.224864118629227</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.008041047715134</v>
+      </c>
+      <c r="T2" t="n">
+        <v>6.938520173244285</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2.634107092212518</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.9063329047579285</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.9615953205607499</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.9580933100354999</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.8346028479422305</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2.45003057069662</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>2.197845619003404</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>8.486510256823196</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>2.913161556938303</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.8989850648115174</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0.9602261217963468</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0.9608964677358998</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0.8373182367070328</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0.02384429277247596</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0.2379410893266969</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.01231873333688077</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0.01457921849559185</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0.02577634566399084</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>0.2251669149984703</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>0.2613597536411247</v>
+      </c>
+      <c r="AO2" t="inlineStr">
         <is>
           <t>RSL</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="AP2" t="inlineStr">
         <is>
           <t>RF</t>
         </is>
       </c>
-      <c r="S2" t="n">
+      <c r="AQ2" t="n">
         <v>3</v>
       </c>
-      <c r="T2" t="n">
+      <c r="AR2" t="n">
         <v>1</v>
       </c>
-      <c r="U2" t="n">
+      <c r="AS2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -604,67 +796,139 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.343892139626848</v>
+        <v>0.3775524332206992</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2230663331919223</v>
+        <v>0.2685076060278524</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2356419066078327</v>
+        <v>0.2750020584353208</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4854296103533783</v>
+        <v>0.5244063867224739</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9579751643431793</v>
+        <v>0.9561245521416009</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9812790588521851</v>
+        <v>0.981246645096184</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9837398423783709</v>
+        <v>0.982540269382874</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8940987088862096</v>
+        <v>0.8898660031811101</v>
       </c>
       <c r="J3" t="n">
-        <v>0.006429351756002399</v>
+        <v>0.3281052121702395</v>
       </c>
       <c r="K3" t="n">
-        <v>0.03503800377535099</v>
+        <v>0.2807725241750751</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4905222417987176</v>
+        <v>0.1611317011068505</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4908528900862456</v>
+        <v>0.4014121337314687</v>
       </c>
       <c r="N3" t="n">
-        <v>0.4424067102513683</v>
+        <v>0.9710956956862766</v>
       </c>
       <c r="O3" t="n">
-        <v>0.02796484541104102</v>
+        <v>0.9867654911701839</v>
       </c>
       <c r="P3" t="n">
-        <v>0.02907201263037898</v>
-      </c>
-      <c r="Q3" t="inlineStr">
+        <v>0.9825873010834181</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.8992622389120642</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.2448823347770864</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.163381188377173</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.1216952679002304</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.3488484884591452</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.9588417205255128</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.9862436069529995</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.9827527423144496</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.8890772133163056</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0.4744774316848343</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.3539226270441689</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.4076333364599421</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.638461695374078</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.9414123215674547</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.984271095111857</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.9879911958578097</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.9098489562997084</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.009265595813057692</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.06042448231947425</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.004234983372056023</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0.005718799858999812</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0.01690761749726066</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0.04491188575807614</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>0.04415011970239147</v>
+      </c>
+      <c r="AO3" t="inlineStr">
         <is>
           <t>WL</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="AP3" t="inlineStr">
         <is>
           <t>RF</t>
         </is>
       </c>
-      <c r="S3" t="n">
+      <c r="AQ3" t="n">
         <v>3</v>
       </c>
-      <c r="T3" t="n">
+      <c r="AR3" t="n">
         <v>1</v>
       </c>
-      <c r="U3" t="n">
+      <c r="AS3" t="n">
         <v>1</v>
       </c>
     </row>
@@ -673,67 +937,139 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.004246402559115</v>
+        <v>1.122946961555754</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6533151361243474</v>
+        <v>0.7045302503516391</v>
       </c>
       <c r="D4" t="n">
-        <v>2.181140751438905</v>
+        <v>2.862181826431843</v>
       </c>
       <c r="E4" t="n">
-        <v>1.476868562682172</v>
+        <v>1.691798400055941</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9655579373772604</v>
+        <v>0.9595143274458552</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9826499920294473</v>
+        <v>0.979554567151771</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9798325984678875</v>
+        <v>0.9742786088644899</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8858549257429758</v>
+        <v>0.8739735258656599</v>
       </c>
       <c r="J4" t="n">
-        <v>0.005274014617128675</v>
+        <v>1.382173897633039</v>
       </c>
       <c r="K4" t="n">
-        <v>0.115462903812495</v>
+        <v>1.117901681247783</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4924987778326415</v>
+        <v>3.46826305224768</v>
       </c>
       <c r="M4" t="n">
-        <v>0.488438318779115</v>
+        <v>1.862327321457665</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4391066256589525</v>
+        <v>0.9588106388979017</v>
       </c>
       <c r="O4" t="n">
-        <v>0.08457620544518557</v>
+        <v>0.9805822358325096</v>
       </c>
       <c r="P4" t="n">
-        <v>0.06597945405567851</v>
-      </c>
-      <c r="Q4" t="inlineStr">
+        <v>0.9771605028452078</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.8986064433619868</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.3252226643289</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.7058662283786021</v>
+      </c>
+      <c r="T4" t="n">
+        <v>4.410069440529714</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2.100016533394371</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.8919174825615341</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.9565368308561661</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.949918300059504</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.8336267089218387</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0.9083202195138784</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.608752251321901</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.720731560721566</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.311766580120704</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.9779649415887585</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.989818988864429</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.9862160203049519</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.910333349871899</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.009334392931756363</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.223114815595726</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.004790392060752879</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0.005798744729279215</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.01415445583992636</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0.1595790820469653</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0.1541671796548533</v>
+      </c>
+      <c r="AO4" t="inlineStr">
         <is>
           <t>DI</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="AP4" t="inlineStr">
         <is>
           <t>RF</t>
         </is>
       </c>
-      <c r="S4" t="n">
+      <c r="AQ4" t="n">
         <v>3</v>
       </c>
-      <c r="T4" t="n">
+      <c r="AR4" t="n">
         <v>1</v>
       </c>
-      <c r="U4" t="n">
+      <c r="AS4" t="n">
         <v>1</v>
       </c>
     </row>
